--- a/040625-skills.xlsx
+++ b/040625-skills.xlsx
@@ -924,72 +924,72 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,99 +997,103 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1350,7 +1354,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="50.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="50.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="17.71"/>
@@ -4091,7 +4095,7 @@
       <c r="G75" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H75" s="0" t="s">
+      <c r="H75" s="26" t="s">
         <v>72</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -4110,7 +4114,7 @@
         <v>47</v>
       </c>
       <c r="R75" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>103</v>
@@ -4165,228 +4169,228 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="42.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="35.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="26" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="26" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="26" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="26" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26"/>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="26" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="26" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="26" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="26" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="26" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27"/>
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="26" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="26" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="26" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="26" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="26" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="26" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="26" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="26" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="26" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="26" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="26" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="26" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="26" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="26" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="26" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="26" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="26" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="26" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="26" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="26" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="26" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="26" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="26" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4410,112 +4414,112 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34" t="s">
+      <c r="T1" s="35"/>
+      <c r="U1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="34" t="s">
+      <c r="V1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
     </row>
     <row r="3" customFormat="false" ht="127.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36" t="s">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="38" t="n">
         <v>45893</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40" t="s">
+      <c r="E3" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="N3" s="41"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40" t="s">
+      <c r="N3" s="42"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="26" t="s">
         <v>103</v>
       </c>
     </row>
